--- a/04_DESIGN_TABLES/DesignTable_6402.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6402.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,6 +504,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,10 +517,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="C3" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="D3" t="n">
         <v>0.5600000000000001</v>
@@ -557,7 +562,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1724 = 1.310 (table had 1.29) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1724 = 0.970 (table had 0.95) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.29 -&gt; OMi 1.310 (Items!L1724, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 0.95 -&gt; OMi 0.970 (Items!P1724, M021)</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -578,10 +588,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="C4" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="D4" t="n">
         <v>0.5600000000000001</v>
@@ -623,7 +633,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1725 = 1.410 (table had 1.43) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1725 = 1.040 (table had 1.06) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.43 -&gt; OMi 1.410 (Items!L1725, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.06 -&gt; OMi 1.040 (Items!P1725, M021)</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -644,10 +659,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="D5" t="n">
         <v>0.6899999999999999</v>
@@ -689,7 +704,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1726 Side 1 ID = 0.172 (table had 0.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1726 Side 1 ID = 0.172 (table had 0.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1726 = 1.410 (table had 1.34) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1726 = 1.070 (table had 1) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.34 -&gt; OMi 1.410 (Items!L1726, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1 -&gt; OMi 1.070 (Items!P1726, M021)</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -710,10 +730,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="C6" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="D6" t="n">
         <v>0.6899999999999999</v>
@@ -755,7 +775,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1727 = 1.430 (table had 1.48) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1727 = 1.050 (table had 1.11) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.48 -&gt; OMi 1.430 (Items!L1727, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.11 -&gt; OMi 1.050 (Items!P1727, M021)</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -776,10 +801,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="C7" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="D7" t="n">
         <v>0.75</v>
@@ -821,7 +846,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1728 = 1.620 (table had 1.48) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1728 = 1.200 (table had 1.06) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.48 -&gt; OMi 1.620 (Items!L1728, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.06 -&gt; OMi 1.200 (Items!P1728, M021)</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -908,10 +938,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="C9" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="D9" t="n">
         <v>0.88</v>
@@ -953,7 +983,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1729 = 1.580 (table had 1.55) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1729 = 1.210 (table had 1.18) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.55 -&gt; OMi 1.580 (Items!L1729, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.18 -&gt; OMi 1.210 (Items!P1729, M021)</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -974,10 +1009,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="C10" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="D10" t="n">
         <v>0.88</v>
@@ -1019,7 +1054,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1730 = 1.650 (table had 1.59) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1730 = 1.230 (table had 1.17) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.59 -&gt; OMi 1.650 (Items!L1730, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.17 -&gt; OMi 1.230 (Items!P1730, M021)</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1040,10 +1080,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="C11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="D11" t="n">
         <v>0.875</v>
@@ -1085,7 +1125,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); C4HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1731 Hex Flat = 0.875 (table had 0.94); D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1731 Side 2 ID = 0.391 (table had 0.48) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); C4HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1731 Hex Flat = 0.875 (table had 0.94); D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1731 Side 2 ID = 0.391 (table had 0.48) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1731 = 1.800 (table had 1.81) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1731 = 1.300 (table had 1.31) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.81 -&gt; OMi 1.800 (Items!L1731, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.31 -&gt; OMi 1.300 (Items!P1731, M021)</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1172,10 +1217,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="C13" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -1217,7 +1262,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1732 = 1.790 (table had 1.72) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1732 = 1.370 (table had 1.3) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.72 -&gt; OMi 1.790 (Items!L1732, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.3 -&gt; OMi 1.370 (Items!P1732, M021)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1238,10 +1288,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="C14" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -1283,7 +1333,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1733 = 1.890 (table had 1.95) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1733 = 1.390 (table had 1.45) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.95 -&gt; OMi 1.890 (Items!L1733, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.45 -&gt; OMi 1.390 (Items!P1733, M021)</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1370,10 +1425,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="C16" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="D16" t="n">
         <v>1.25</v>
@@ -1415,7 +1470,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1736 = 2.140 (table had 2.17) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1736 = 1.580 (table had 1.61) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.17 -&gt; OMi 2.140 (Items!L1736, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.61 -&gt; OMi 1.580 (Items!P1736, M021)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1568,10 +1628,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="C19" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="D19" t="n">
         <v>1.5</v>
@@ -1613,7 +1673,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1738 = 2.260 (table had 2.28) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1738 = 1.670 (table had 1.69) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.28 -&gt; OMi 2.260 (Items!L1738, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.69 -&gt; OMi 1.670 (Items!P1738, M021)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1700,10 +1765,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="C21" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="D21" t="n">
         <v>1.88</v>
@@ -1745,7 +1810,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1739 = 2.420 (table had 2.45) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1739 = 1.800 (table had 1.83) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.45 -&gt; OMi 2.420 (Items!L1739, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.83 -&gt; OMi 1.800 (Items!P1739, M021)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1832,10 +1902,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.72</v>
+        <v>2.61</v>
       </c>
       <c r="C23" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="D23" t="n">
         <v>2.13</v>
@@ -1877,7 +1947,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1740 = 2.610 (table had 2.72) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1740 = 1.870 (table had 1.99) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.72 -&gt; OMi 2.610 (Items!L1740, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.99 -&gt; OMi 1.870 (Items!P1740, M021)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -1898,10 +1973,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="C24" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="D24" t="n">
         <v>2.75</v>
@@ -1943,7 +2018,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag)</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1741 = 2.950 (table had 2.93) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1741 = 2.010 (table had 1.99) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.93 -&gt; OMi 2.950 (Items!L1741, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.99 -&gt; OMi 2.010 (Items!P1741, M021)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -1954,6 +2034,77 @@
       <c r="Q24" t="inlineStr">
         <is>
           <t>6402-32-32-O</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6402-12-10-O</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>6402-12-10-O</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (B (1) UN/UNF-2A) x 7/8-14 (B (2) UN/UNF-2B)</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; L26 / L27 / body hex / nut hex / bores: OMi WebsitePartsInfo2026 Items (= Brennan TFA p.15 on every cell, one source); ORB end from the ORB library; JIC swivel from SWIV_MEAS</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from OMi Items (= the Brennan TFA catalog p.15, one source)</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>6402-12-10-O</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_6402.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6402.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="C3" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="D3" t="n">
         <v>0.5600000000000001</v>
@@ -562,12 +562,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1724 = 1.310 (table had 1.29) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1724 = 0.970 (table had 0.95) [user 2026-10-18 A19]</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1724 = 1.310 (table had 1.29) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1724 = 0.970 (table had 0.95) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 1.29 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.31) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 0.95 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.97) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.29 -&gt; OMi 1.310 (Items!L1724, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 0.95 -&gt; OMi 0.970 (Items!P1724, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.29 -&gt; OMi 1.310 (Items!L1724, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 0.95 -&gt; OMi 0.970 (Items!P1724, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 1.31 -&gt; Air-Way 1.29 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 0.97 -&gt; Air-Way 0.95</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="C4" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="D4" t="n">
         <v>0.5600000000000001</v>
@@ -633,12 +633,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1725 = 1.410 (table had 1.43) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1725 = 1.040 (table had 1.06) [user 2026-10-18 A19]</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1725 = 1.410 (table had 1.43) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1725 = 1.040 (table had 1.06) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 1.43 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.41) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.06 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.04) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.43 -&gt; OMi 1.410 (Items!L1725, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.06 -&gt; OMi 1.040 (Items!P1725, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.43 -&gt; OMi 1.410 (Items!L1725, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.06 -&gt; OMi 1.040 (Items!P1725, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 1.41 -&gt; Air-Way 1.43 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.04 -&gt; Air-Way 1.06</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="C5" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>0.6899999999999999</v>
@@ -671,7 +671,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.172</v>
+        <v>0.3</v>
       </c>
       <c r="G5" t="n">
         <v>0.17</v>
@@ -704,12 +704,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1726 Side 1 ID = 0.172 (table had 0.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1726 = 1.410 (table had 1.34) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1726 = 1.070 (table had 1) [user 2026-10-18 A19]</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1726 Side 1 ID = 0.172 (table had 0.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1726 = 1.410 (table had 1.34) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1726 = 1.070 (table had 1) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 1.34 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.41) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.07) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 0.3 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.172) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.34 -&gt; OMi 1.410 (Items!L1726, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1 -&gt; OMi 1.070 (Items!P1726, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.34 -&gt; OMi 1.410 (Items!L1726, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1 -&gt; OMi 1.070 (Items!P1726, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 1.41 -&gt; Air-Way 1.34 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.07 -&gt; Air-Way 1 | 2026-10-20 Air-Way first: D1@BORE OMi/Brennan 0.172 -&gt; Air-Way 0.3</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="C6" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="D6" t="n">
         <v>0.6899999999999999</v>
@@ -775,12 +775,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1727 = 1.430 (table had 1.48) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1727 = 1.050 (table had 1.11) [user 2026-10-18 A19]</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1727 = 1.430 (table had 1.48) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1727 = 1.050 (table had 1.11) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 1.48 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.43) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.11 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.05) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.48 -&gt; OMi 1.430 (Items!L1727, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.11 -&gt; OMi 1.050 (Items!P1727, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.48 -&gt; OMi 1.430 (Items!L1727, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.11 -&gt; OMi 1.050 (Items!P1727, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 1.43 -&gt; Air-Way 1.48 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.05 -&gt; Air-Way 1.11</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="C7" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="D7" t="n">
         <v>0.75</v>
@@ -846,12 +846,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1728 = 1.620 (table had 1.48) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1728 = 1.200 (table had 1.06) [user 2026-10-18 A19]</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1728 = 1.620 (table had 1.48) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1728 = 1.200 (table had 1.06) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 1.48 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.62) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.06 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.2) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.48 -&gt; OMi 1.620 (Items!L1728, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.06 -&gt; OMi 1.200 (Items!P1728, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.48 -&gt; OMi 1.620 (Items!L1728, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.06 -&gt; OMi 1.200 (Items!P1728, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 1.62 -&gt; Air-Way 1.48 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.2 -&gt; Air-Way 1.06</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="C9" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="D9" t="n">
         <v>0.88</v>
@@ -983,12 +983,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1729 = 1.580 (table had 1.55) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1729 = 1.210 (table had 1.18) [user 2026-10-18 A19]</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1729 = 1.580 (table had 1.55) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1729 = 1.210 (table had 1.18) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 1.55 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.58) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.18 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.21) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.55 -&gt; OMi 1.580 (Items!L1729, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.18 -&gt; OMi 1.210 (Items!P1729, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.55 -&gt; OMi 1.580 (Items!L1729, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.18 -&gt; OMi 1.210 (Items!P1729, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 1.58 -&gt; Air-Way 1.55 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.21 -&gt; Air-Way 1.18</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="C10" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="D10" t="n">
         <v>0.88</v>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1730 = 1.650 (table had 1.59) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1730 = 1.230 (table had 1.17) [user 2026-10-18 A19]</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1730 = 1.650 (table had 1.59) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1730 = 1.230 (table had 1.17) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 1.59 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.65) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.17 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.23) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.59 -&gt; OMi 1.650 (Items!L1730, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.17 -&gt; OMi 1.230 (Items!P1730, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.59 -&gt; OMi 1.650 (Items!L1730, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.17 -&gt; OMi 1.230 (Items!P1730, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 1.65 -&gt; Air-Way 1.59 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.23 -&gt; Air-Way 1.17</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1080,13 +1080,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="C11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="D11" t="n">
-        <v>0.875</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -1095,7 +1095,7 @@
         <v>0.39</v>
       </c>
       <c r="G11" t="n">
-        <v>0.391</v>
+        <v>0.48</v>
       </c>
       <c r="H11" t="n">
         <v>0.75</v>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); C4HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1731 Hex Flat = 0.875 (table had 0.94); D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1731 Side 2 ID = 0.391 (table had 0.48) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1731 = 1.800 (table had 1.81) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1731 = 1.300 (table had 1.31) [user 2026-10-18 A19]</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); C4HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1731 Hex Flat = 0.875 (table had 0.94); D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1731 Side 2 ID = 0.391 (table had 0.48) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1731 = 1.800 (table had 1.81) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1731 = 1.300 (table had 1.31) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 1.81 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.8) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.31 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.3) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C4HEX@HEX: Air-Way 0.94 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.875) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D2@BORE: Air-Way 0.48 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.391) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.81 -&gt; OMi 1.800 (Items!L1731, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.31 -&gt; OMi 1.300 (Items!P1731, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.81 -&gt; OMi 1.800 (Items!L1731, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.31 -&gt; OMi 1.300 (Items!P1731, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 1.8 -&gt; Air-Way 1.81 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.3 -&gt; Air-Way 1.31 | 2026-10-20 Air-Way first: C4HEX@HEX OMi/Brennan 0.875 -&gt; Air-Way 0.94 | 2026-10-20 Air-Way first: D2@BORE OMi/Brennan 0.391 -&gt; Air-Way 0.48</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1217,10 +1217,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="C13" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1732 = 1.790 (table had 1.72) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1732 = 1.370 (table had 1.3) [user 2026-10-18 A19]</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1732 = 1.790 (table had 1.72) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1732 = 1.370 (table had 1.3) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 1.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.79) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.3 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.37) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.72 -&gt; OMi 1.790 (Items!L1732, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.3 -&gt; OMi 1.370 (Items!P1732, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.72 -&gt; OMi 1.790 (Items!L1732, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.3 -&gt; OMi 1.370 (Items!P1732, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 1.79 -&gt; Air-Way 1.72 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.37 -&gt; Air-Way 1.3</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="C14" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1733 = 1.890 (table had 1.95) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1733 = 1.390 (table had 1.45) [user 2026-10-18 A19]</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1733 = 1.890 (table had 1.95) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1733 = 1.390 (table had 1.45) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 1.95 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.89) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.45 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.39) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.95 -&gt; OMi 1.890 (Items!L1733, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.45 -&gt; OMi 1.390 (Items!P1733, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 1.95 -&gt; OMi 1.890 (Items!L1733, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.45 -&gt; OMi 1.390 (Items!P1733, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 1.89 -&gt; Air-Way 1.95 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.39 -&gt; Air-Way 1.45</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="C16" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="D16" t="n">
         <v>1.25</v>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1736 = 2.140 (table had 2.17) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1736 = 1.580 (table had 1.61) [user 2026-10-18 A19]</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1736 = 2.140 (table had 2.17) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1736 = 1.580 (table had 1.61) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 2.17 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.14) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.61 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.58) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.17 -&gt; OMi 2.140 (Items!L1736, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.61 -&gt; OMi 1.580 (Items!P1736, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.17 -&gt; OMi 2.140 (Items!L1736, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.61 -&gt; OMi 1.580 (Items!P1736, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 2.14 -&gt; Air-Way 2.17 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.58 -&gt; Air-Way 1.61</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="C19" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="D19" t="n">
         <v>1.5</v>
@@ -1673,12 +1673,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1738 = 2.260 (table had 2.28) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1738 = 1.670 (table had 1.69) [user 2026-10-18 A19]</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1738 = 2.260 (table had 2.28) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1738 = 1.670 (table had 1.69) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 2.28 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.26) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.69 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.67) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.28 -&gt; OMi 2.260 (Items!L1738, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.69 -&gt; OMi 1.670 (Items!P1738, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.28 -&gt; OMi 2.260 (Items!L1738, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.69 -&gt; OMi 1.670 (Items!P1738, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 2.26 -&gt; Air-Way 2.28 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.67 -&gt; Air-Way 1.69</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="C21" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="D21" t="n">
         <v>1.88</v>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1739 = 2.420 (table had 2.45) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1739 = 1.800 (table had 1.83) [user 2026-10-18 A19]</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1739 = 2.420 (table had 2.45) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1739 = 1.800 (table had 1.83) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 2.45 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.42) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.83 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.8) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.45 -&gt; OMi 2.420 (Items!L1739, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.83 -&gt; OMi 1.800 (Items!P1739, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.45 -&gt; OMi 2.420 (Items!L1739, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.83 -&gt; OMi 1.800 (Items!P1739, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 2.42 -&gt; Air-Way 2.45 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.8 -&gt; Air-Way 1.83</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.61</v>
+        <v>2.72</v>
       </c>
       <c r="C23" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="D23" t="n">
         <v>2.13</v>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1740 = 2.610 (table had 2.72) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1740 = 1.870 (table had 1.99) [user 2026-10-18 A19]</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1740 = 2.610 (table had 2.72) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1740 = 1.870 (table had 1.99) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 2.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.61) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.99 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.87) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.72 -&gt; OMi 2.610 (Items!L1740, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.99 -&gt; OMi 1.870 (Items!P1740, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.72 -&gt; OMi 2.610 (Items!L1740, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.99 -&gt; OMi 1.870 (Items!P1740, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 2.61 -&gt; Air-Way 2.72 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 1.87 -&gt; Air-Way 1.99</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="C24" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="D24" t="n">
         <v>2.75</v>
@@ -2018,12 +2018,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1741 = 2.950 (table had 2.93) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1741 = 2.010 (table had 1.99) [user 2026-10-18 A19]</t>
+          <t>Air-Way s92 only (double-pass 22 rows); "-O" suffix kept verbatim; 6402-6-8-O TUBE OD 1/2, 6402-8-12-O TUBE OD 1 (do not match -6/-8 first end; copied as printed); 6402-24-20-O L26/L27 1.90/1.27 far below siblings (flag); L26@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1741 = 2.950 (table had 2.93) [user 2026-10-18 A19]; L27@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!P1741 = 2.010 (table had 1.99) [user 2026-10-18 A19]; L26@DRIVE: Air-Way 2.93 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.95) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; L27@DRIVE: Air-Way 1.99 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.01) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.93 -&gt; OMi 2.950 (Items!L1741, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.99 -&gt; OMi 2.010 (Items!P1741, M021)</t>
+          <t>A19 (user 2026-10-18, group 3 open): L26@DRIVE 2.93 -&gt; OMi 2.950 (Items!L1741, M020) | A19 (user 2026-10-18, group 3 open): L27@DRIVE 1.99 -&gt; OMi 2.010 (Items!P1741, M021) | 2026-10-20 Air-Way first: L26@DRIVE OMi/Brennan 2.95 -&gt; Air-Way 2.93 | 2026-10-20 Air-Way first: L27@DRIVE OMi/Brennan 2.01 -&gt; Air-Way 1.99</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
